--- a/task197/golden/site_response_scorecard.xlsx
+++ b/task197/golden/site_response_scorecard.xlsx
@@ -688,7 +688,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Under tolerance</t>
+          <t>Below 90% tolerance</t>
         </is>
       </c>
     </row>
@@ -1386,10 +1386,10 @@
         <v>1168</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>1157</v>
+        <v>1151</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7">
@@ -1405,10 +1405,10 @@
         <v>1428</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>1416.5</v>
+        <v>1407.1</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>11.5</v>
+        <v>20.9</v>
       </c>
     </row>
     <row r="8">
@@ -1443,10 +1443,10 @@
         <v>1642</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>1625.5</v>
+        <v>1615.5</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>16.5</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="10">
@@ -1462,10 +1462,10 @@
         <v>252</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>247</v>
+        <v>244.2</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>5</v>
+        <v>7.8</v>
       </c>
     </row>
   </sheetData>
@@ -1536,10 +1536,10 @@
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>20.2</v>
+        <v>22</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>50.7</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="6">
@@ -1554,10 +1554,10 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>8.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>17.8</v>
+        <v>18.6</v>
       </c>
     </row>
     <row r="7">
@@ -1572,10 +1572,10 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>22.5</v>
+        <v>21.9</v>
       </c>
     </row>
     <row r="8">
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>10.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>15.8</v>
+        <v>16.1</v>
       </c>
     </row>
     <row r="9">
@@ -1608,7 +1608,7 @@
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>11.3</v>
+        <v>10.9</v>
       </c>
       <c r="D9" s="7" t="n">
         <v>28</v>
@@ -1626,10 +1626,10 @@
         </is>
       </c>
       <c r="C10" s="7" t="n">
-        <v>9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>24.2</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="11">
@@ -1644,10 +1644,10 @@
         </is>
       </c>
       <c r="C11" s="7" t="n">
-        <v>11.2</v>
+        <v>11.6</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
     </row>
     <row r="12">
@@ -1662,7 +1662,7 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>15.6</v>
+        <v>15.3</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>22.1</v>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="C13" s="7" t="n">
-        <v>16.5</v>
+        <v>16.3</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>48.6</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="15">
@@ -1694,10 +1694,10 @@
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="n">
-        <v>113.7</v>
+        <v>114.4</v>
       </c>
       <c r="D15" t="n">
-        <v>247.8</v>
+        <v>242.6</v>
       </c>
     </row>
   </sheetData>

--- a/task197/golden/site_response_scorecard.xlsx
+++ b/task197/golden/site_response_scorecard.xlsx
@@ -25,7 +25,7 @@
     <numFmt numFmtId="164" formatCode="0.0#"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -47,6 +47,10 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <sz val="8"/>
     </font>
   </fonts>
   <fills count="3">
@@ -79,7 +83,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -90,6 +94,7 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1479,7 +1484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1698,6 +1703,13 @@
       </c>
       <c r="D15" t="n">
         <v>242.6</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>Portfolio totals are rounded once from the unrounded period sums, per clause 5, so they need not equal the sum of the rounded rows above.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1711,7 +1723,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A23"/>
+  <dimension ref="A1:A25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="92" customWidth="1" min="1" max="1"/>
@@ -1820,39 +1832,53 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>delivery dates and rounded once. Episode counts are whole.</t>
+          <t>delivery dates and rounded once. A portfolio total is rounded once from the unrounded</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr"/>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>period sums, so it need not equal the sum of the rounded rows it sits under. Episode</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>counts are whole.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>Meppelerdiep had no qualifying over-frequency episode in the window, so its</t>
         </is>
       </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>down-regulation gain is reported as none rather than as zero.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>down-regulation gain is reported as none rather than as zero.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>The Oosterhout metering point was replaced at the connection with effect from</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>2026-10-01; both codes are its own and both are included.</t>
         </is>

--- a/task197/golden/site_response_scorecard.xlsx
+++ b/task197/golden/site_response_scorecard.xlsx
@@ -718,7 +718,7 @@
         <v>72</v>
       </c>
       <c r="F5" t="n">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -747,7 +747,7 @@
         <v>83</v>
       </c>
       <c r="F6" t="n">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
         <v>88</v>
       </c>
       <c r="F7" t="n">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         <v>91</v>
       </c>
       <c r="F8" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
         <v>93</v>
       </c>
       <c r="F9" t="n">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -863,7 +863,7 @@
         <v>95</v>
       </c>
       <c r="F10" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>97</v>
       </c>
       <c r="F11" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>99</v>
       </c>
       <c r="F12" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         <v>101</v>
       </c>
       <c r="F13" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         <v>87</v>
       </c>
       <c r="D6" t="n">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="7">
@@ -1222,7 +1222,7 @@
         <v>89</v>
       </c>
       <c r="D9" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10">
@@ -1258,7 +1258,7 @@
         <v>81</v>
       </c>
       <c r="D11" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12">
@@ -1276,7 +1276,7 @@
         <v>98</v>
       </c>
       <c r="D12" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13">
@@ -1294,7 +1294,7 @@
         <v>94</v>
       </c>
       <c r="D13" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>

--- a/task197/golden/site_response_scorecard.xlsx
+++ b/task197/golden/site_response_scorecard.xlsx
@@ -834,7 +834,7 @@
         <v>93</v>
       </c>
       <c r="F9" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>98</v>
       </c>
       <c r="D12" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13">
